--- a/AAII_Financials/Yearly/KSPI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KSPI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>KSPI</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -662,8 +662,7 @@
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -696,11 +695,11 @@
       <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="I7" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J7" s="2">
+        <v>43100</v>
       </c>
       <c r="K7" s="2"/>
     </row>
@@ -709,25 +708,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1733700</v>
+        <v>4196200</v>
       </c>
       <c r="E8" s="3">
-        <v>1194800</v>
+        <v>2744000</v>
       </c>
       <c r="F8" s="3">
-        <v>877900</v>
+        <v>2036200</v>
       </c>
       <c r="G8" s="3">
-        <v>671700</v>
+        <v>1431000</v>
       </c>
       <c r="H8" s="3">
-        <v>545700</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>1342500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>977400</v>
+      </c>
+      <c r="J8" s="3">
+        <v>828800</v>
       </c>
       <c r="K8" s="3"/>
     </row>
@@ -735,26 +734,26 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>427500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>226900</v>
+      </c>
+      <c r="F9" s="3">
+        <v>168700</v>
+      </c>
+      <c r="G9" s="3">
+        <v>143200</v>
+      </c>
+      <c r="H9" s="3">
+        <v>145500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>109400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>98900</v>
       </c>
       <c r="K9" s="3"/>
     </row>
@@ -762,26 +761,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>3768800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2517100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1867500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1287800</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1197100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>868100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>729800</v>
       </c>
       <c r="K10" s="3"/>
     </row>
@@ -802,26 +801,26 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>195500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>130000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>102100</v>
+      </c>
+      <c r="G12" s="3">
+        <v>69300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>49400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>38300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>37600</v>
       </c>
       <c r="K12" s="3"/>
     </row>
@@ -856,26 +855,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3"/>
     </row>
@@ -883,26 +882,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>58000</v>
       </c>
       <c r="E15" s="3">
-        <v>-5900</v>
+        <v>37700</v>
       </c>
       <c r="F15" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>29200</v>
+      </c>
+      <c r="G15" s="3">
+        <v>22800</v>
+      </c>
+      <c r="H15" s="3">
+        <v>19600</v>
+      </c>
+      <c r="I15" s="3">
+        <v>13500</v>
+      </c>
+      <c r="J15" s="3">
+        <v>16300</v>
       </c>
       <c r="K15" s="3"/>
     </row>
@@ -921,25 +920,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1159900</v>
+        <v>911900</v>
       </c>
       <c r="E17" s="3">
-        <v>694500</v>
+        <v>585100</v>
       </c>
       <c r="F17" s="3">
-        <v>428200</v>
+        <v>424300</v>
       </c>
       <c r="G17" s="3">
-        <v>346600</v>
+        <v>346700</v>
       </c>
       <c r="H17" s="3">
-        <v>326600</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>408200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>357800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>282100</v>
       </c>
       <c r="K17" s="3"/>
     </row>
@@ -948,25 +947,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>573800</v>
+        <v>3284300</v>
       </c>
       <c r="E18" s="3">
-        <v>500300</v>
+        <v>2158800</v>
       </c>
       <c r="F18" s="3">
-        <v>449700</v>
+        <v>1611900</v>
       </c>
       <c r="G18" s="3">
-        <v>325100</v>
+        <v>1084300</v>
       </c>
       <c r="H18" s="3">
-        <v>219100</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>934300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>619600</v>
+      </c>
+      <c r="J18" s="3">
+        <v>546700</v>
       </c>
       <c r="K18" s="3"/>
     </row>
@@ -988,19 +987,19 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1552000</v>
+        <v>-24000</v>
       </c>
       <c r="E20" s="3">
-        <v>998500</v>
+        <v>-3000</v>
       </c>
       <c r="F20" s="3">
-        <v>650200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>336000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>278300</v>
+        <v>1500</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1015,25 +1014,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2125800</v>
+        <v>3366400</v>
       </c>
       <c r="E21" s="3">
-        <v>1498800</v>
+        <v>2199500</v>
       </c>
       <c r="F21" s="3">
-        <v>1099900</v>
+        <v>1639500</v>
       </c>
       <c r="G21" s="3">
-        <v>661100</v>
+        <v>1107100</v>
       </c>
       <c r="H21" s="3">
-        <v>497400</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>953900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>633100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>563000</v>
       </c>
       <c r="K21" s="3"/>
     </row>
@@ -1042,25 +1041,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>1054300</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>602500</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>394400</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>329900</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>309600</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>267400</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>291900</v>
       </c>
       <c r="K22" s="3"/>
     </row>
@@ -1069,25 +1068,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2125800</v>
+        <v>2254100</v>
       </c>
       <c r="E23" s="3">
-        <v>1498800</v>
+        <v>1557800</v>
       </c>
       <c r="F23" s="3">
-        <v>1099900</v>
+        <v>1216000</v>
       </c>
       <c r="G23" s="3">
-        <v>661100</v>
+        <v>754400</v>
       </c>
       <c r="H23" s="3">
-        <v>497400</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>624700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>352200</v>
+      </c>
+      <c r="J23" s="3">
+        <v>254800</v>
       </c>
       <c r="K23" s="3"/>
     </row>
@@ -1096,25 +1095,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>360300</v>
+        <v>382100</v>
       </c>
       <c r="E24" s="3">
-        <v>274000</v>
+        <v>284800</v>
       </c>
       <c r="F24" s="3">
-        <v>194700</v>
+        <v>215200</v>
       </c>
       <c r="G24" s="3">
-        <v>113300</v>
+        <v>129300</v>
       </c>
       <c r="H24" s="3">
-        <v>87400</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>109800</v>
+      </c>
+      <c r="I24" s="3">
+        <v>62800</v>
+      </c>
+      <c r="J24" s="3">
+        <v>40500</v>
       </c>
       <c r="K24" s="3"/>
     </row>
@@ -1150,25 +1149,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1765400</v>
+        <v>1872000</v>
       </c>
       <c r="E26" s="3">
-        <v>1224800</v>
+        <v>1273100</v>
       </c>
       <c r="F26" s="3">
-        <v>905200</v>
+        <v>1000800</v>
       </c>
       <c r="G26" s="3">
-        <v>547800</v>
+        <v>625100</v>
       </c>
       <c r="H26" s="3">
-        <v>410000</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>515000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>289400</v>
+      </c>
+      <c r="J26" s="3">
+        <v>214300</v>
       </c>
       <c r="K26" s="3"/>
     </row>
@@ -1177,25 +1176,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1750000</v>
+        <v>1855600</v>
       </c>
       <c r="E27" s="3">
-        <v>1216900</v>
+        <v>1264800</v>
       </c>
       <c r="F27" s="3">
-        <v>898400</v>
+        <v>993200</v>
       </c>
       <c r="G27" s="3">
-        <v>542800</v>
+        <v>619400</v>
       </c>
       <c r="H27" s="3">
-        <v>403100</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>506300</v>
+      </c>
+      <c r="I27" s="3">
+        <v>274900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>147300</v>
       </c>
       <c r="K27" s="3"/>
     </row>
@@ -1312,19 +1311,19 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1552000</v>
+        <v>24000</v>
       </c>
       <c r="E32" s="3">
-        <v>-998500</v>
+        <v>3000</v>
       </c>
       <c r="F32" s="3">
-        <v>-650200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-336000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-278300</v>
+        <v>-1500</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1339,25 +1338,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1750000</v>
+        <v>1855600</v>
       </c>
       <c r="E33" s="3">
-        <v>1216900</v>
+        <v>1264800</v>
       </c>
       <c r="F33" s="3">
-        <v>898400</v>
+        <v>993200</v>
       </c>
       <c r="G33" s="3">
-        <v>542800</v>
+        <v>619400</v>
       </c>
       <c r="H33" s="3">
-        <v>403100</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>506300</v>
+      </c>
+      <c r="I33" s="3">
+        <v>274900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>196200</v>
       </c>
       <c r="K33" s="3"/>
     </row>
@@ -1393,25 +1392,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1750000</v>
+        <v>1855600</v>
       </c>
       <c r="E35" s="3">
-        <v>1216900</v>
+        <v>1264800</v>
       </c>
       <c r="F35" s="3">
-        <v>898400</v>
+        <v>993200</v>
       </c>
       <c r="G35" s="3">
-        <v>542800</v>
+        <v>619400</v>
       </c>
       <c r="H35" s="3">
-        <v>403100</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>506300</v>
+      </c>
+      <c r="I35" s="3">
+        <v>274900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>196200</v>
       </c>
       <c r="K35" s="3"/>
     </row>
@@ -1439,11 +1438,11 @@
       <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="I38" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J38" s="2">
+        <v>43100</v>
       </c>
       <c r="K38" s="2"/>
     </row>
@@ -1478,25 +1477,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1272900</v>
+        <v>1809600</v>
       </c>
       <c r="E41" s="3">
-        <v>924700</v>
+        <v>1330400</v>
       </c>
       <c r="F41" s="3">
-        <v>825400</v>
+        <v>786700</v>
       </c>
       <c r="G41" s="3">
-        <v>540800</v>
+        <v>784300</v>
       </c>
       <c r="H41" s="3">
-        <v>387800</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>624700</v>
+      </c>
+      <c r="I41" s="3">
+        <v>438700</v>
+      </c>
+      <c r="J41" s="3">
+        <v>916200</v>
       </c>
       <c r="K41" s="3"/>
     </row>
@@ -1505,25 +1504,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>595500</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>498000</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>60100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>296000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>252600</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3"/>
     </row>
@@ -1532,25 +1531,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>9419400</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>6883600</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>5728800</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>3442200</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>3493800</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>2845800</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>2709700</v>
       </c>
       <c r="K43" s="3"/>
     </row>
@@ -1558,26 +1557,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3"/>
     </row>
@@ -1586,25 +1585,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>67300</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>63500</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>25900</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>59000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>25800</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>13700</v>
       </c>
       <c r="K45" s="3"/>
     </row>
@@ -1613,25 +1612,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>11400200</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>8370300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>6616700</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>4351100</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>4210300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>3363400</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>3672200</v>
       </c>
       <c r="K46" s="3"/>
     </row>
@@ -1640,25 +1639,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>3037300</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>2326800</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>1394600</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>2055200</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>1236300</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>928900</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>638700</v>
       </c>
       <c r="K47" s="3"/>
     </row>
@@ -1667,25 +1666,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>330300</v>
+        <v>314800</v>
       </c>
       <c r="E48" s="3">
-        <v>277400</v>
+        <v>251900</v>
       </c>
       <c r="F48" s="3">
-        <v>186200</v>
+        <v>163200</v>
       </c>
       <c r="G48" s="3">
-        <v>125200</v>
+        <v>142900</v>
       </c>
       <c r="H48" s="3">
-        <v>109800</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>137900</v>
+      </c>
+      <c r="I48" s="3">
+        <v>75400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>76400</v>
       </c>
       <c r="K48" s="3"/>
     </row>
@@ -1694,25 +1693,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>65800</v>
+        <v>144900</v>
       </c>
       <c r="E49" s="3">
-        <v>31800</v>
+        <v>33100</v>
       </c>
       <c r="F49" s="3">
-        <v>29400</v>
+        <v>32500</v>
       </c>
       <c r="G49" s="3">
-        <v>20400</v>
+        <v>23300</v>
       </c>
       <c r="H49" s="3">
-        <v>17100</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>21400</v>
+      </c>
+      <c r="I49" s="3">
+        <v>20200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>20300</v>
       </c>
       <c r="K49" s="3"/>
     </row>
@@ -1774,26 +1773,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>148800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>90700</v>
+      </c>
+      <c r="F52" s="3">
+        <v>89700</v>
       </c>
       <c r="G52" s="3">
-        <v>17900</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>89700</v>
+      </c>
+      <c r="H52" s="3">
+        <v>108900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>38400</v>
+      </c>
+      <c r="J52" s="3">
+        <v>18900</v>
       </c>
       <c r="K52" s="3"/>
     </row>
@@ -1829,25 +1828,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>14189600</v>
+        <v>15046000</v>
       </c>
       <c r="E54" s="3">
-        <v>10653000</v>
+        <v>11072800</v>
       </c>
       <c r="F54" s="3">
-        <v>7504500</v>
+        <v>8296700</v>
       </c>
       <c r="G54" s="3">
-        <v>5838000</v>
+        <v>6662200</v>
       </c>
       <c r="H54" s="3">
-        <v>4550200</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>5714800</v>
+      </c>
+      <c r="I54" s="3">
+        <v>4426300</v>
+      </c>
+      <c r="J54" s="3">
+        <v>4426500</v>
       </c>
       <c r="K54" s="3"/>
     </row>
@@ -1881,14 +1880,14 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>103300</v>
-      </c>
-      <c r="E57" s="3">
-        <v>49000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>25100</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -1909,25 +1908,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>34800</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>173700</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>24300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>30800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>116700</v>
       </c>
       <c r="K58" s="3"/>
     </row>
@@ -1936,25 +1935,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>81100</v>
+        <v>2390600</v>
       </c>
       <c r="E59" s="3">
-        <v>75400</v>
+        <v>1925300</v>
       </c>
       <c r="F59" s="3">
-        <v>69500</v>
+        <v>1520300</v>
       </c>
       <c r="G59" s="3">
-        <v>38100</v>
+        <v>1148700</v>
       </c>
       <c r="H59" s="3">
-        <v>20400</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>772000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>447000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>268400</v>
       </c>
       <c r="K59" s="3"/>
     </row>
@@ -1963,25 +1962,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>2424300</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1989500</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1715200</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1191000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>790600</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>486600</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>392900</v>
       </c>
       <c r="K60" s="3"/>
     </row>
@@ -1990,25 +1989,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>336600</v>
+        <v>356900</v>
       </c>
       <c r="E61" s="3">
-        <v>432600</v>
+        <v>450300</v>
       </c>
       <c r="F61" s="3">
-        <v>431300</v>
+        <v>479100</v>
       </c>
       <c r="G61" s="3">
-        <v>451600</v>
+        <v>491100</v>
       </c>
       <c r="H61" s="3">
-        <v>450000</v>
+        <v>565200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>562300</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>689100</v>
       </c>
       <c r="K61" s="3"/>
     </row>
@@ -2017,25 +2016,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6600</v>
+        <v>9810900</v>
       </c>
       <c r="E62" s="3">
-        <v>6700</v>
+        <v>6831000</v>
       </c>
       <c r="F62" s="3">
-        <v>5200</v>
+        <v>4927100</v>
       </c>
       <c r="G62" s="3">
-        <v>4800</v>
+        <v>4030600</v>
       </c>
       <c r="H62" s="3">
-        <v>4900</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>3572500</v>
+      </c>
+      <c r="I62" s="3">
+        <v>2812200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2749000</v>
       </c>
       <c r="K62" s="3"/>
     </row>
@@ -2125,25 +2124,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11947100</v>
+        <v>12612800</v>
       </c>
       <c r="E66" s="3">
-        <v>8949200</v>
+        <v>9287700</v>
       </c>
       <c r="F66" s="3">
-        <v>6465000</v>
+        <v>7136200</v>
       </c>
       <c r="G66" s="3">
-        <v>5024500</v>
+        <v>5725400</v>
       </c>
       <c r="H66" s="3">
-        <v>3942700</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>4942600</v>
+      </c>
+      <c r="I66" s="3">
+        <v>3869200</v>
+      </c>
+      <c r="J66" s="3">
+        <v>3852900</v>
       </c>
       <c r="K66" s="3"/>
     </row>
@@ -2237,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>82300</v>
       </c>
       <c r="K70" s="3"/>
     </row>
@@ -2273,25 +2272,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2194300</v>
+        <v>2326700</v>
       </c>
       <c r="E72" s="3">
-        <v>1586000</v>
+        <v>1648500</v>
       </c>
       <c r="F72" s="3">
-        <v>785900</v>
+        <v>868900</v>
       </c>
       <c r="G72" s="3">
-        <v>584100</v>
+        <v>666600</v>
       </c>
       <c r="H72" s="3">
-        <v>406100</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>510000</v>
+      </c>
+      <c r="I72" s="3">
+        <v>371900</v>
+      </c>
+      <c r="J72" s="3">
+        <v>141900</v>
       </c>
       <c r="K72" s="3"/>
     </row>
@@ -2381,25 +2380,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2242500</v>
+        <v>2377800</v>
       </c>
       <c r="E76" s="3">
-        <v>1703900</v>
+        <v>1771000</v>
       </c>
       <c r="F76" s="3">
-        <v>1039400</v>
+        <v>1149200</v>
       </c>
       <c r="G76" s="3">
-        <v>813500</v>
+        <v>928400</v>
       </c>
       <c r="H76" s="3">
-        <v>607400</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>762900</v>
+      </c>
+      <c r="I76" s="3">
+        <v>524700</v>
+      </c>
+      <c r="J76" s="3">
+        <v>462000</v>
       </c>
       <c r="K76" s="3"/>
     </row>
@@ -2454,11 +2453,11 @@
       <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="I80" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J80" s="2">
+        <v>43100</v>
       </c>
       <c r="K80" s="2"/>
     </row>
@@ -2467,25 +2466,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1750000</v>
+        <v>1855600</v>
       </c>
       <c r="E81" s="3">
-        <v>1216900</v>
+        <v>1264800</v>
       </c>
       <c r="F81" s="3">
-        <v>898400</v>
+        <v>993200</v>
       </c>
       <c r="G81" s="3">
-        <v>542800</v>
+        <v>619400</v>
       </c>
       <c r="H81" s="3">
-        <v>403100</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>506300</v>
+      </c>
+      <c r="I81" s="3">
+        <v>274900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>196200</v>
       </c>
       <c r="K81" s="3"/>
     </row>
@@ -2507,25 +2506,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>46300</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+        <v>28700</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>16600</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>15200</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>16300</v>
       </c>
       <c r="K83" s="3"/>
     </row>
@@ -2669,25 +2668,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2300700</v>
+        <v>2439600</v>
       </c>
       <c r="E89" s="3">
-        <v>2123600</v>
+        <v>2207300</v>
       </c>
       <c r="F89" s="3">
-        <v>146300</v>
+        <v>161800</v>
       </c>
       <c r="G89" s="3">
-        <v>1284900</v>
+        <v>1466300</v>
       </c>
       <c r="H89" s="3">
-        <v>616400</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>774200</v>
+      </c>
+      <c r="I89" s="3">
+        <v>92900</v>
+      </c>
+      <c r="J89" s="3">
+        <v>425500</v>
       </c>
       <c r="K89" s="3"/>
     </row>
@@ -2709,25 +2708,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-104500</v>
+        <v>-110800</v>
       </c>
       <c r="E91" s="3">
-        <v>-123700</v>
+        <v>-128600</v>
       </c>
       <c r="F91" s="3">
-        <v>-51800</v>
+        <v>-57300</v>
       </c>
       <c r="G91" s="3">
-        <v>-37800</v>
+        <v>-43200</v>
       </c>
       <c r="H91" s="3">
-        <v>-35200</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-44200</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-15800</v>
       </c>
       <c r="K91" s="3"/>
     </row>
@@ -2790,25 +2789,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-454200</v>
+        <v>-481600</v>
       </c>
       <c r="E94" s="3">
-        <v>-1013300</v>
+        <v>-1053200</v>
       </c>
       <c r="F94" s="3">
-        <v>602700</v>
+        <v>666300</v>
       </c>
       <c r="G94" s="3">
-        <v>-758600</v>
+        <v>-865700</v>
       </c>
       <c r="H94" s="3">
-        <v>-234700</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-294800</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-336700</v>
+      </c>
+      <c r="J94" s="3">
+        <v>78900</v>
       </c>
       <c r="K94" s="3"/>
     </row>
@@ -2830,25 +2829,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1165100</v>
+        <v>1235400</v>
       </c>
       <c r="E96" s="3">
-        <v>-437000</v>
+        <v>454200</v>
       </c>
       <c r="F96" s="3">
-        <v>-708000</v>
+        <v>782700</v>
       </c>
       <c r="G96" s="3">
-        <v>-364800</v>
+        <v>416300</v>
       </c>
       <c r="H96" s="3">
-        <v>-203200</v>
+        <v>255200</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>45600</v>
       </c>
       <c r="K96" s="3"/>
     </row>
@@ -2938,25 +2937,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1406000</v>
+        <v>-1490900</v>
       </c>
       <c r="E100" s="3">
-        <v>-573900</v>
+        <v>-596500</v>
       </c>
       <c r="F100" s="3">
-        <v>-733400</v>
+        <v>-810800</v>
       </c>
       <c r="G100" s="3">
-        <v>-369200</v>
+        <v>-421300</v>
       </c>
       <c r="H100" s="3">
-        <v>-233500</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>-293200</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-148600</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-61400</v>
       </c>
       <c r="K100" s="3"/>
     </row>
@@ -2965,25 +2964,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-13900</v>
+        <v>-14800</v>
       </c>
       <c r="E101" s="3">
-        <v>31900</v>
+        <v>33200</v>
       </c>
       <c r="F101" s="3">
-        <v>8700</v>
+        <v>9600</v>
       </c>
       <c r="G101" s="3">
-        <v>32700</v>
+        <v>37400</v>
       </c>
       <c r="H101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>-1500</v>
+      </c>
+      <c r="I101" s="3">
+        <v>37300</v>
+      </c>
+      <c r="J101" s="3">
+        <v>100</v>
       </c>
       <c r="K101" s="3"/>
     </row>
@@ -2992,25 +2991,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>426600</v>
+        <v>452400</v>
       </c>
       <c r="E102" s="3">
-        <v>568400</v>
+        <v>590800</v>
       </c>
       <c r="F102" s="3">
-        <v>24300</v>
+        <v>26900</v>
       </c>
       <c r="G102" s="3">
-        <v>189800</v>
+        <v>216600</v>
       </c>
       <c r="H102" s="3">
-        <v>147000</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>184600</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-355100</v>
+      </c>
+      <c r="J102" s="3">
+        <v>443200</v>
       </c>
       <c r="K102" s="3"/>
     </row>

--- a/AAII_Financials/Yearly/KSPI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KSPI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>KSPI</t>
   </si>
@@ -656,135 +656,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4849600</v>
+      </c>
+      <c r="E8" s="3">
         <v>4196200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2744000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2036200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1431000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1342500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>977400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>828800</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>427500</v>
+        <v>632900</v>
       </c>
       <c r="E9" s="3">
-        <v>226900</v>
+        <v>424700</v>
       </c>
       <c r="F9" s="3">
+        <v>224600</v>
+      </c>
+      <c r="G9" s="3">
         <v>168700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>143200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>145500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>109400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>98900</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>3768800</v>
+        <v>4216700</v>
       </c>
       <c r="E10" s="3">
-        <v>2517100</v>
+        <v>3771600</v>
       </c>
       <c r="F10" s="3">
+        <v>2519400</v>
+      </c>
+      <c r="G10" s="3">
         <v>1867500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1287800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1197100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>868100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>729800</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -796,35 +808,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>195500</v>
+        <v>197900</v>
       </c>
       <c r="E12" s="3">
-        <v>130000</v>
+        <v>186900</v>
       </c>
       <c r="F12" s="3">
+        <v>124400</v>
+      </c>
+      <c r="G12" s="3">
         <v>102100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>69300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>49400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>38300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>37600</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -849,20 +865,23 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>1500</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -876,36 +895,42 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E15" s="3">
         <v>58000</v>
       </c>
-      <c r="E15" s="3">
-        <v>37700</v>
-      </c>
       <c r="F15" s="3">
+        <v>36300</v>
+      </c>
+      <c r="G15" s="3">
         <v>29200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>22800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16300</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -914,62 +939,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1208000</v>
+      </c>
+      <c r="E17" s="3">
         <v>911900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>585100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>424300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>346700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>408200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>357800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>282100</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3641500</v>
+      </c>
+      <c r="E18" s="3">
         <v>3284300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2158800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1611900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1084300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>934300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>619600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>546700</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -981,22 +1013,23 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-24000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1500</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1007,117 +1040,132 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3673600</v>
+      </c>
+      <c r="E21" s="3">
         <v>3366400</v>
       </c>
-      <c r="E21" s="3">
-        <v>2199500</v>
-      </c>
       <c r="F21" s="3">
+        <v>2198100</v>
+      </c>
+      <c r="G21" s="3">
         <v>1639500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1107100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>953900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>633100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>563000</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1174400</v>
+      </c>
+      <c r="E22" s="3">
         <v>1054300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>602500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>394400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>329900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>309600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>267400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>291900</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2444300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2254100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1557800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1216000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>754400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>624700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>352200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>254800</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>429800</v>
+      </c>
+      <c r="E24" s="3">
         <v>382100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>284800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>215200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>129300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>109800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>62800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>40500</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1142,63 +1190,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2014500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1872000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1273100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1000800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>625100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>515000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>289400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>214300</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1981900</v>
+      </c>
+      <c r="E27" s="3">
         <v>1855600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1264800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>993200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>619400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>506300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>274900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>147300</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1223,9 +1280,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1250,9 +1310,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1277,9 +1340,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1304,23 +1370,26 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E32" s="3">
         <v>24000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1331,36 +1400,42 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1981900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1855600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1264800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>993200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>619400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>506300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>274900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>196200</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1385,68 +1460,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1981900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1855600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1264800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>993200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>619400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>506300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>274900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>196200</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1458,8 +1542,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1471,35 +1556,39 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1180800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1809600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1330400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>786700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>784300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>624700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>438700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>916200</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1524,44 +1613,50 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9419400</v>
+        <v>11042700</v>
       </c>
       <c r="E43" s="3">
+        <v>9433600</v>
+      </c>
+      <c r="F43" s="3">
         <v>6883600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5728800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3442200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3493800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2845800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2709700</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>31700</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1578,144 +1673,162 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>67400</v>
+      </c>
+      <c r="E45" s="3">
         <v>67300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>63500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>59000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13700</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11400200</v>
+        <v>12431000</v>
       </c>
       <c r="E46" s="3">
+        <v>11446000</v>
+      </c>
+      <c r="F46" s="3">
         <v>8370300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6616700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4351100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4210300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3363400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3672200</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2839600</v>
+      </c>
+      <c r="E47" s="3">
         <v>3037300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2326800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1394600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2055200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1236300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>928900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>638700</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>368300</v>
+      </c>
+      <c r="E48" s="3">
         <v>314800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>251900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>163200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>142900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>137900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>75400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>76400</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>178300</v>
+      </c>
+      <c r="E49" s="3">
         <v>144900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>33100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>32500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>21400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>20200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>20300</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1740,9 +1853,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1767,36 +1883,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>148800</v>
+        <v>151100</v>
       </c>
       <c r="E52" s="3">
+        <v>103000</v>
+      </c>
+      <c r="F52" s="3">
         <v>90700</v>
-      </c>
-      <c r="F52" s="3">
-        <v>89700</v>
       </c>
       <c r="G52" s="3">
         <v>89700</v>
       </c>
       <c r="H52" s="3">
+        <v>89700</v>
+      </c>
+      <c r="I52" s="3">
         <v>108900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>38400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18900</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1821,36 +1943,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15968200</v>
+      </c>
+      <c r="E54" s="3">
         <v>15046000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11072800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8296700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6662200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5714800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4426300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4426500</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1862,8 +1990,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1875,8 +2004,9 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -1901,144 +2031,162 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>262100</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>34800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>173700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>24300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>30800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>116700</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2157500</v>
+      </c>
+      <c r="E59" s="3">
         <v>2390600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1925300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1520300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1148700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>772000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>447000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>268400</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2424300</v>
+        <v>2459700</v>
       </c>
       <c r="E60" s="3">
+        <v>2430600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1989500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1715200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1191000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>790600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>486600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>392900</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>356900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>450300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>479100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>491100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>565200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>562300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>689100</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>9810900</v>
+        <v>10459900</v>
       </c>
       <c r="E62" s="3">
+        <v>9777200</v>
+      </c>
+      <c r="F62" s="3">
         <v>6831000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4927100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4030600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3572500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2812200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2749000</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2063,9 +2211,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2090,9 +2241,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2117,36 +2271,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12970100</v>
+      </c>
+      <c r="E66" s="3">
         <v>12612800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9287700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7136200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5725400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4942600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3869200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3852900</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2158,8 +2318,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2184,9 +2345,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2211,9 +2375,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2236,11 +2403,14 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>82300</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2265,36 +2435,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2793100</v>
+      </c>
+      <c r="E72" s="3">
         <v>2326700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1648500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>868900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>666600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>510000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>371900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>141900</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2319,9 +2495,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2346,9 +2525,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2373,36 +2555,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2892100</v>
+      </c>
+      <c r="E76" s="3">
         <v>2377800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1771000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1149200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>928400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>762900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>524700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>462000</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2427,68 +2615,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1981900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1855600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1264800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>993200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>619400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>506300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>274900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>196200</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2500,35 +2697,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E83" s="3">
         <v>46300</v>
       </c>
-      <c r="E83" s="3">
-        <v>28700</v>
-      </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="3">
+        <v>36300</v>
+      </c>
+      <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>16300</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2553,9 +2754,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2580,9 +2784,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2607,9 +2814,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2634,9 +2844,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2661,36 +2874,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1109200</v>
+      </c>
+      <c r="E89" s="3">
         <v>2439600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2207300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>161800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1466300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>774200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>92900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>425500</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2702,35 +2921,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-182500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-110800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-128600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-57300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-43200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-44200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-15800</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2755,9 +2978,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2782,36 +3008,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-206600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-481600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1053200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>666300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-865700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-294800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-336700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>78900</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2823,35 +3055,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1231500</v>
+      </c>
+      <c r="E96" s="3">
         <v>1235400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>454200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>782700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>416300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>255200</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>45600</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2876,9 +3112,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2903,9 +3142,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2930,88 +3172,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1352900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1490900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-596500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-810800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-421300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-293200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-148600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-61400</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>67200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-14800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>33200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>37400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>37300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-383100</v>
+      </c>
+      <c r="E102" s="3">
         <v>452400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>590800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>216600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>184600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-355100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>443200</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/KSPI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KSPI_YR_FIN.xlsx
@@ -656,147 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7976700</v>
+      </c>
+      <c r="E8" s="3">
         <v>4849600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4196200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2744000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2036200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1431000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1342500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>977400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>828800</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2385500</v>
+      </c>
+      <c r="E9" s="3">
         <v>632900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>424700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>224600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>168700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>143200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>145500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>109400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>98900</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5591200</v>
+      </c>
+      <c r="E10" s="3">
         <v>4216700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3771600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2519400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1867500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1287800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1197100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>868100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>729800</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,38 +821,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>392300</v>
+      </c>
+      <c r="E12" s="3">
         <v>197900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>186900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>124400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>102100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>69300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>49400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>38300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>37600</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,9 +884,12 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -880,11 +899,11 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>1500</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -898,39 +917,45 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>54900</v>
+        <v>154400</v>
       </c>
       <c r="E15" s="3">
-        <v>58000</v>
+        <v>55000</v>
       </c>
       <c r="F15" s="3">
+        <v>56400</v>
+      </c>
+      <c r="G15" s="3">
         <v>36300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>29200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>22800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>13500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16300</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -940,68 +965,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3561800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1208000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>911900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>585100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>424300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>346700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>408200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>357800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>282100</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4414900</v>
+      </c>
+      <c r="E18" s="3">
         <v>3641500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3284300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2158800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1611900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1084300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>934300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>619600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>546700</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1014,25 +1046,26 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E20" s="3">
         <v>22800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-24000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1500</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1043,129 +1076,144 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3673600</v>
+        <v>4574700</v>
       </c>
       <c r="E21" s="3">
-        <v>3366400</v>
+        <v>3673700</v>
       </c>
       <c r="F21" s="3">
+        <v>3364700</v>
+      </c>
+      <c r="G21" s="3">
         <v>2198100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1639500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1107100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>953900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>633100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>563000</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1792700</v>
+      </c>
+      <c r="E22" s="3">
         <v>1174400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1054300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>602500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>394400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>329900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>309600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>267400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>291900</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2627600</v>
+      </c>
+      <c r="E23" s="3">
         <v>2444300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2254100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1557800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1216000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>754400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>624700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>352200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>254800</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>521200</v>
+      </c>
+      <c r="E24" s="3">
         <v>429800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>382100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>284800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>215200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>129300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>109800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>62800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>40500</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1193,69 +1241,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2106400</v>
+      </c>
+      <c r="E26" s="3">
         <v>2014500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1872000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1273100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1000800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>625100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>515000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>289400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>214300</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2117200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1981900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1855600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1264800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>993200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>619400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>506300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>274900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>147300</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1283,9 +1340,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1313,9 +1373,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1343,9 +1406,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1373,26 +1439,29 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-22800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>24000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1403,39 +1472,45 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2117200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1981900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1855600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1264800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>993200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>619400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>506300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>274900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>196200</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1463,74 +1538,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2117200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1981900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1855600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1264800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>993200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>619400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>506300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>274900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>196200</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1543,8 +1627,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1557,43 +1642,47 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1781700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1180800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1809600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1330400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>786700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>784300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>624700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>438700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>916200</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>42800</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1616,50 +1705,56 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14343600</v>
+      </c>
+      <c r="E43" s="3">
         <v>11042700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9433600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6883600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5728800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3442200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3493800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2845800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2709700</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>30900</v>
+        <v>245700</v>
       </c>
       <c r="E44" s="3">
+        <v>30800</v>
+      </c>
+      <c r="F44" s="3">
         <v>31700</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
@@ -1676,159 +1771,177 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>67400</v>
+        <v>26700</v>
       </c>
       <c r="E45" s="3">
+        <v>66200</v>
+      </c>
+      <c r="F45" s="3">
         <v>67300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>63500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>59000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13700</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12431000</v>
+        <v>17042500</v>
       </c>
       <c r="E46" s="3">
+        <v>12429800</v>
+      </c>
+      <c r="F46" s="3">
         <v>11446000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8370300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6616700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4351100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4210300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3363400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3672200</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2283200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2839600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3037300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2326800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1394600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2055200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1236300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>928900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>638700</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>619300</v>
+      </c>
+      <c r="E48" s="3">
         <v>368300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>314800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>251900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>163200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>142900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>137900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>75400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>76400</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1672100</v>
+      </c>
+      <c r="E49" s="3">
         <v>178300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>144900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>33100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>32500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>21400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>20200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>20300</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1856,9 +1969,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1886,39 +2002,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>151100</v>
+        <v>165200</v>
       </c>
       <c r="E52" s="3">
+        <v>152300</v>
+      </c>
+      <c r="F52" s="3">
         <v>103000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>90700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>89700</v>
       </c>
       <c r="H52" s="3">
         <v>89700</v>
       </c>
       <c r="I52" s="3">
+        <v>89700</v>
+      </c>
+      <c r="J52" s="3">
         <v>108900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18900</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1946,39 +2068,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21862000</v>
+      </c>
+      <c r="E54" s="3">
         <v>15968200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15046000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11072800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8296700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6662200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5714800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4426300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4426500</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1991,8 +2119,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2005,16 +2134,17 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>683400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>42800</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -2034,159 +2164,177 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>262100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>34800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>173700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>30800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>116700</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2261500</v>
+      </c>
+      <c r="E59" s="3">
         <v>2157500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2390600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1925300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1520300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1148700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>772000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>447000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>268400</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2459700</v>
+        <v>3021600</v>
       </c>
       <c r="E60" s="3">
+        <v>2502500</v>
+      </c>
+      <c r="F60" s="3">
         <v>2430600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1989500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1715200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1191000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>790600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>486600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>392900</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>697900</v>
+      </c>
+      <c r="E61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>356900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>450300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>479100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>491100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>565200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>562300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>689100</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10459900</v>
+        <v>12698900</v>
       </c>
       <c r="E62" s="3">
+        <v>10417100</v>
+      </c>
+      <c r="F62" s="3">
         <v>9777200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6831000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4927100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4030600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3572500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2812200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2749000</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2214,9 +2362,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2244,9 +2395,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2274,39 +2428,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16729600</v>
+      </c>
+      <c r="E66" s="3">
         <v>12970100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12612800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9287700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7136200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5725400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4942600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3869200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3852900</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2319,8 +2479,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2348,9 +2509,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2378,9 +2542,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2406,11 +2573,14 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>82300</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2438,39 +2608,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5018400</v>
+      </c>
+      <c r="E72" s="3">
         <v>2793100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2326700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1648500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>868900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>666600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>510000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>371900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>141900</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2498,9 +2674,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2528,9 +2707,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2558,39 +2740,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4915900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2892100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2377800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1771000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1149200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>928400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>762900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>524700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>462000</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2618,74 +2806,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2117200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1981900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1855600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1264800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>993200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>619400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>506300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>274900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>196200</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2698,38 +2895,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>46100</v>
+        <v>104000</v>
       </c>
       <c r="E83" s="3">
-        <v>46300</v>
+        <v>46200</v>
       </c>
       <c r="F83" s="3">
+        <v>56400</v>
+      </c>
+      <c r="G83" s="3">
         <v>36300</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>15200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>16300</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2757,9 +2958,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2787,9 +2991,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2817,9 +3024,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2847,9 +3057,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2877,39 +3090,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1328900</v>
+      </c>
+      <c r="E89" s="3">
         <v>1109200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2439600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2207300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>161800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1466300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>774200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>92900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>425500</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2922,38 +3141,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-360100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-182500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-110800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-128600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-57300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-43200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-44200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-15800</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2981,9 +3204,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3011,39 +3237,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1001800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-206600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-481600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1053200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>666300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-865700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-294800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-336700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>78900</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3056,38 +3288,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>1231500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1235400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>454200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>782700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>416300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>255200</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>45600</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3115,9 +3351,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3145,9 +3384,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3175,97 +3417,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>296400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1352900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1490900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-596500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-810800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-421300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-293200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-148600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-61400</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="E101" s="3">
         <v>67200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-14800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>33200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>37400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>37300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>559600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-383100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>452400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>590800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>26900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>216600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>184600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-355100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>443200</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
